--- a/news_push_data/all_news/cnyes/20260403 鉅亨網新聞.xlsx
+++ b/news_push_data/all_news/cnyes/20260403 鉅亨網新聞.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,22 +451,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>川普政府公告對鋼鐵、鋁、銅衍生品徵25%關稅 | 鉅亨網 - 美股雷達</t>
+          <t>馬克宏批川普言論 恐削弱北約信任基礎 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-04-03 04:59</t>
+          <t>2026-04-03 02:30</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-03T04:59:21+08:00</t>
+          <t>2026-04-03T02:30:02+08:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6406580</t>
+          <t>https://news.cnyes.com/news/id/6406349</t>
         </is>
       </c>
     </row>
@@ -478,22 +478,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>馬克宏批川普言論 恐削弱北約信任基礎 | 鉅亨網 - 國際政經</t>
+          <t>川普談話引爆油價壓力：美國汽油恐衝5美元、柴油逼近新高 | 鉅亨網 - 能源</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-04-03 02:30</t>
+          <t>2026-04-03 01:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-03T02:30:02+08:00</t>
+          <t>2026-04-03T01:00:05+08:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6406349</t>
+          <t>https://news.cnyes.com/news/id/6406515</t>
         </is>
       </c>
     </row>
@@ -505,22 +505,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>比高油價更傷！專家示警：財富縮水與「CNN效應」恐重挫美國經濟 | 鉅亨網 - 美股雷達</t>
+          <t>川普政府擬對進口藥品課徵最高100%關稅 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-04-03 02:00</t>
+          <t>2026-04-02 23:27</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-03T02:00:02+08:00</t>
+          <t>2026-04-02T23:27:05+08:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405150</t>
+          <t>https://news.cnyes.com/news/id/6406492</t>
         </is>
       </c>
     </row>
@@ -532,22 +532,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>川普談話引爆油價壓力：美國汽油恐衝5美元、柴油逼近新高 | 鉅亨網 - 能源</t>
+          <t>荷姆茲海峽有望恢復通行？伊朗與阿曼研擬監控機制 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-04-03 01:00</t>
+          <t>2026-04-02 23:10</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-03T01:00:05+08:00</t>
+          <t>2026-04-02T23:10:04+08:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6406515</t>
+          <t>https://news.cnyes.com/news/id/6406486</t>
         </is>
       </c>
     </row>
@@ -559,22 +559,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>川普政府擬對進口藥品課徵最高100%關稅 | 鉅亨網 - 國際政經</t>
+          <t>烏克蘭無人機狂襲 俄油港儲油設施損失四成 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-04-02 23:27</t>
+          <t>2026-04-02 22:31</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-02T23:27:05+08:00</t>
+          <t>2026-04-02T22:31:02+08:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6406492</t>
+          <t>https://news.cnyes.com/news/id/6406445</t>
         </is>
       </c>
     </row>
@@ -586,22 +586,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>荷姆茲海峽有望恢復通行？伊朗與阿曼研擬監控機制 | 鉅亨網 - 國際政經</t>
+          <t>油氣價格飆升 生質能源股成資金焦點 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-04-02 23:10</t>
+          <t>2026-04-02 21:32</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-02T23:10:04+08:00</t>
+          <t>2026-04-02T21:32:07+08:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6406486</t>
+          <t>https://news.cnyes.com/news/id/6406421</t>
         </is>
       </c>
     </row>
@@ -613,22 +613,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>烏克蘭無人機狂襲 俄油港儲油設施損失四成 | 鉅亨網 - 國際政經</t>
+          <t>國際油價暴衝10%！川普對伊朗強硬發言 點燃市場避險情緒 | 鉅亨網 - 能源</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-04-02 22:31</t>
+          <t>2026-04-02 21:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-02T22:31:02+08:00</t>
+          <t>2026-04-02T21:00:03+08:00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6406445</t>
+          <t>https://news.cnyes.com/news/id/6406380</t>
         </is>
       </c>
     </row>
@@ -640,22 +640,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>美上周初領失業金人數降至近兩年低點 就業市場陷「低招募、低裁員」 | 鉅亨網 - 美股雷達</t>
+          <t>華爾街看中東戰事：川普談話未釋明確訊號 市場不確定性升溫 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-04-02 22:00</t>
+          <t>2026-04-02 20:30</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-02T22:00:03+08:00</t>
+          <t>2026-04-02T20:30:15+08:00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6406268</t>
+          <t>https://news.cnyes.com/news/id/6406332</t>
         </is>
       </c>
     </row>
@@ -667,22 +667,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>〈美股早盤〉中東戰事降溫希望受挫 主要指數開低、油價勁揚 | 鉅亨網 - 美股雷達</t>
+          <t>川普喊戰事將落幕 市場卻更怕高油價「吃掉需求」 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-04-02 21:42</t>
+          <t>2026-04-02 20:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-02T21:42:03+08:00</t>
+          <t>2026-04-02T20:00:05+08:00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6406266</t>
+          <t>https://news.cnyes.com/news/id/6406270</t>
         </is>
       </c>
     </row>
@@ -694,22 +694,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>油氣價格飆升 生質能源股成資金焦點 | 鉅亨網 - 國際政經</t>
+          <t>川普對伊朗戰事時間表含糊不清 引發市場與政治焦慮 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-04-02 21:32</t>
+          <t>2026-04-02 19:50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-02T21:32:07+08:00</t>
+          <t>2026-04-02T19:50:02+08:00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6406421</t>
+          <t>https://news.cnyes.com/news/id/6406235</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>元太科技篤定入主台虹拿4席董事 陳永恒今以法人代表接任董事長 | 鉅亨網 - 台股新聞</t>
+          <t>禮來減重藥獲批、亞馬遜布局低軌衛星科技與醫療題材同步升溫 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-04-02 21:14</t>
+          <t>2026-04-02 19:30</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-02T21:14:36+08:00</t>
+          <t>2026-04-02T19:30:07+08:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6406395</t>
+          <t>https://news.cnyes.com/news/id/6406303</t>
         </is>
       </c>
     </row>
@@ -748,22 +748,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>國際油價暴衝10%！川普對伊朗強硬發言 點燃市場避險情緒 | 鉅亨網 - 能源</t>
+          <t>烏克蘭無人機打擊 俄羅斯石油出口受阻 減產壓力迫在眉睫 | 鉅亨網 - 能源</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-04-02 21:00</t>
+          <t>2026-04-02 19:20</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-02T21:00:03+08:00</t>
+          <t>2026-04-02T19:20:22+08:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6406380</t>
+          <t>https://news.cnyes.com/news/id/6406271</t>
         </is>
       </c>
     </row>
@@ -775,22 +775,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>華爾街看中東戰事：川普談話未釋明確訊號 市場不確定性升溫 | 鉅亨網 - 國際政經</t>
+          <t>伊朗傳尋求中國安全擔保 北京呼籲美以停止軍事行動 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-04-02 20:30</t>
+          <t>2026-04-02 18:50</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-02T20:30:15+08:00</t>
+          <t>2026-04-02T18:50:03+08:00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6406332</t>
+          <t>https://news.cnyes.com/news/id/6406189</t>
         </is>
       </c>
     </row>
@@ -802,22 +802,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>川普喊戰事將落幕 市場卻更怕高油價「吃掉需求」 | 鉅亨網 - 國際政經</t>
+          <t>【量大強漲股整理】清明變盤轉折出現?關鍵看甚麼?下周主流股就在這!!! | 鉅亨網 - 專家觀點</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-04-02 20:00</t>
+          <t>2026-04-02 18:10</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-02T20:00:05+08:00</t>
+          <t>2026-04-02T18:10:05+08:00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6406270</t>
+          <t>https://news.cnyes.com/news/id/6406201</t>
         </is>
       </c>
     </row>
@@ -829,22 +829,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>川普對伊朗戰事時間表含糊不清 引發市場與政治焦慮 | 鉅亨網 - 國際政經</t>
+          <t>荷姆茲海峽局勢動盪 川普促亞洲自保 各國外交與能源策略現分歧 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-04-02 19:50</t>
+          <t>2026-04-02 17:40</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-02T19:50:02+08:00</t>
+          <t>2026-04-02T17:40:04+08:00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6406235</t>
+          <t>https://news.cnyes.com/news/id/6405893</t>
         </is>
       </c>
     </row>
@@ -856,22 +856,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>禮來減重藥獲批、亞馬遜布局低軌衛星科技與醫療題材同步升溫 | 鉅亨網 - 國際政經</t>
+          <t>川普變數、清明長假雙重夾擊！台股回檔該跑還是加碼？ | 鉅亨網 - 台股新聞</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-04-02 19:30</t>
+          <t>2026-04-02 17:31</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-02T19:30:07+08:00</t>
+          <t>2026-04-02T17:31:41+08:00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6406303</t>
+          <t>https://news.cnyes.com/news/id/6406109</t>
         </is>
       </c>
     </row>
@@ -883,22 +883,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>烏克蘭無人機打擊 俄羅斯石油出口受阻 減產壓力迫在眉睫 | 鉅亨網 - 能源</t>
+          <t>節後才是大舉加碼最佳時機、華通9⊕、兆赫8⊕、鈦昇4⊕、下一檔【拳王鈦昇】請跟上 | 鉅亨網 - 專家觀點</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-04-02 19:20</t>
+          <t>2026-04-02 17:22</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-02T19:20:22+08:00</t>
+          <t>2026-04-02T17:22:21+08:00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6406271</t>
+          <t>https://news.cnyes.com/news/id/6406055</t>
         </is>
       </c>
     </row>
@@ -910,22 +910,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>伊朗傳尋求中國安全擔保 北京呼籲美以停止軍事行動 | 鉅亨網 - 國際政經</t>
+          <t>史無前例的分裂言論！美媒：市場想聽的 川普一句都沒說 只是預告下一場風暴 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-04-02 18:50</t>
+          <t>2026-04-02 17:10</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-02T18:50:03+08:00</t>
+          <t>2026-04-02T17:10:03+08:00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6406189</t>
+          <t>https://news.cnyes.com/news/id/6406023</t>
         </is>
       </c>
     </row>
@@ -937,22 +937,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>【量大強漲股整理】清明變盤轉折出現?關鍵看甚麼?下周主流股就在這!!! | 鉅亨網 - 專家觀點</t>
+          <t>川普揚言未來數週強攻伊朗中東股市早盤普遍走低、沙國逆勢收紅 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-04-02 18:10</t>
+          <t>2026-04-02 17:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-02T18:10:05+08:00</t>
+          <t>2026-04-02T17:00:05+08:00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6406201</t>
+          <t>https://news.cnyes.com/news/id/6406032</t>
         </is>
       </c>
     </row>
@@ -964,22 +964,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>荷姆茲海峽局勢動盪 川普促亞洲自保 各國外交與能源策略現分歧 | 鉅亨網 - 國際政經</t>
+          <t>回應川普演說 伊朗：絕不容忍戰爭、談判、停火的「惡性循環」 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-04-02 17:40</t>
+          <t>2026-04-02 16:40</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-02T17:40:04+08:00</t>
+          <t>2026-04-02T16:40:04+08:00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405893</t>
+          <t>https://news.cnyes.com/news/id/6405997</t>
         </is>
       </c>
     </row>
@@ -991,22 +991,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>川普變數、清明長假雙重夾擊！台股回檔該跑還是加碼？ | 鉅亨網 - 台股新聞</t>
+          <t>實施『較低風險』的策略 獲利+10萬/2天！ | 鉅亨網 - 台股新聞</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-04-02 17:31</t>
+          <t>2026-04-02 16:23</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-02T17:31:41+08:00</t>
+          <t>2026-04-02T16:23:47+08:00</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6406109</t>
+          <t>https://news.cnyes.com/news/id/6405954</t>
         </is>
       </c>
     </row>
@@ -1018,22 +1018,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>節後才是大舉加碼最佳時機、華通9⊕、兆赫8⊕、鈦昇4⊕、下一檔【拳王鈦昇】請跟上 | 鉅亨網 - 專家觀點</t>
+          <t>伊朗擊落16架「死神」無人機 美軍損失近4.8億美元 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-04-02 17:22</t>
+          <t>2026-04-02 16:20</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-02T17:22:21+08:00</t>
+          <t>2026-04-02T16:20:08+08:00</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6406055</t>
+          <t>https://news.cnyes.com/news/id/6405759</t>
         </is>
       </c>
     </row>
@@ -1045,22 +1045,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>史無前例的分裂言論！美媒：市場想聽的 川普一句都沒說 只是預告下一場風暴 | 鉅亨網 - 國際政經</t>
+          <t>高盛重磅解讀「十五五」規劃：中國GDP鎖定4.4% 告別房地產依賴 點名四大賽道 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-04-02 17:10</t>
+          <t>2026-04-02 16:20</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-02T17:10:03+08:00</t>
+          <t>2026-04-02T16:20:04+08:00</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6406023</t>
+          <t>https://news.cnyes.com/news/id/6405754</t>
         </is>
       </c>
     </row>
@@ -1072,22 +1072,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>川普揚言未來數週強攻伊朗中東股市早盤普遍走低、沙國逆勢收紅 | 鉅亨網 - 國際政經</t>
+          <t>每逢周四必定大跌 標普500已建立「戰爭模式」？ | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-04-02 17:00</t>
+          <t>2026-04-02 16:18</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-02T17:00:05+08:00</t>
+          <t>2026-04-02T16:18:04+08:00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6406032</t>
+          <t>https://news.cnyes.com/news/id/6405848</t>
         </is>
       </c>
     </row>
@@ -1099,22 +1099,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>回應川普演說 伊朗：絕不容忍戰爭、談判、停火的「惡性循環」 | 鉅亨網 - 國際政經</t>
+          <t>Krispy Kreme搭阿提米絲二號熱潮限時推聯名甜甜圈搶攻話題商機 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-04-02 16:40</t>
+          <t>2026-04-02 15:31</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-02T16:40:04+08:00</t>
+          <t>2026-04-02T15:31:27+08:00</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405997</t>
+          <t>https://news.cnyes.com/news/id/6405909</t>
         </is>
       </c>
     </row>
@@ -1126,22 +1126,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>實施『較低風險』的策略 獲利+10萬/2天！ | 鉅亨網 - 台股新聞</t>
+          <t>川普揚言持續打擊伊朗全球股市重挫、油價衝破100美元 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-04-02 16:23</t>
+          <t>2026-04-02 15:31</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-02T16:23:47+08:00</t>
+          <t>2026-04-02T15:31:26+08:00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405954</t>
+          <t>https://news.cnyes.com/news/id/6405907</t>
         </is>
       </c>
     </row>
@@ -1153,22 +1153,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>伊朗擊落16架「死神」無人機 美軍損失近4.8億美元 | 鉅亨網 - 國際政經</t>
+          <t>NASA發射阿提米絲二號睽違逾50年再啟載人繞月任務 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-04-02 16:20</t>
+          <t>2026-04-02 15:31</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-02T16:20:08+08:00</t>
+          <t>2026-04-02T15:31:26+08:00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405759</t>
+          <t>https://news.cnyes.com/news/id/6405905</t>
         </is>
       </c>
     </row>
@@ -1180,22 +1180,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>高盛重磅解讀「十五五」規劃：中國GDP鎖定4.4% 告別房地產依賴 點名四大賽道 | 鉅亨網 - 國際政經</t>
+          <t>專家：川普若「無協議」停戰 伊朗或成最後贏家 海灣國家陷戰略危局 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-04-02 16:20</t>
+          <t>2026-04-02 15:20</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-02T16:20:04+08:00</t>
+          <t>2026-04-02T15:20:05+08:00</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405754</t>
+          <t>https://news.cnyes.com/news/id/6405788</t>
         </is>
       </c>
     </row>
@@ -1207,22 +1207,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>每逢周四必定大跌 標普500已建立「戰爭模式」？ | 鉅亨網 - 國際政經</t>
+          <t>4/10 CPI開獎有多慘? 通膨預期與遞延發酵才是重點 | 鉅亨網 - 專家觀點</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-04-02 16:18</t>
+          <t>2026-04-02 13:58</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-02T16:18:04+08:00</t>
+          <t>2026-04-02T13:58:26+08:00</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405848</t>
+          <t>https://news.cnyes.com/news/id/6405770</t>
         </is>
       </c>
     </row>
@@ -1234,22 +1234,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Krispy Kreme搭阿提米絲二號熱潮限時推聯名甜甜圈搶攻話題商機 | 鉅亨網 - 國際政經</t>
+          <t>民主黨怒轟川普演說「混亂可悲」 對伊朗戰略是史上最大失敗 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-04-02 15:31</t>
+          <t>2026-04-02 13:57</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-02T15:31:27+08:00</t>
+          <t>2026-04-02T13:57:52+08:00</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405909</t>
+          <t>https://news.cnyes.com/news/id/6405756</t>
         </is>
       </c>
     </row>
@@ -1261,22 +1261,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>川普揚言持續打擊伊朗全球股市重挫、油價衝破100美元 | 鉅亨網 - 國際政經</t>
+          <t>油價飆升惹民怨！民調：川普經濟支持率降至31% 創任內新低 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-04-02 15:31</t>
+          <t>2026-04-02 13:20</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-02T15:31:26+08:00</t>
+          <t>2026-04-02T13:20:08+08:00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405907</t>
+          <t>https://news.cnyes.com/news/id/6405699</t>
         </is>
       </c>
     </row>
@@ -1288,22 +1288,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NASA發射阿提米絲二號睽違逾50年再啟載人繞月任務 | 鉅亨網 - 國際政經</t>
+          <t>中東衝突成人民幣國際化破局之戰！德銀：石油美元面臨危機 人民幣迎來關鍵窗口期 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-04-02 15:31</t>
+          <t>2026-04-02 13:20</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-02T15:31:26+08:00</t>
+          <t>2026-04-02T13:20:04+08:00</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405905</t>
+          <t>https://news.cnyes.com/news/id/6405195</t>
         </is>
       </c>
     </row>
@@ -1315,22 +1315,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>專家：川普若「無協議」停戰 伊朗或成最後贏家 海灣國家陷戰略危局 | 鉅亨網 - 國際政經</t>
+          <t>美國低估伊朗？專家：伊朗戰爭恐比越戰更棘手 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-04-02 15:20</t>
+          <t>2026-04-02 13:01</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-02T15:20:05+08:00</t>
+          <t>2026-04-02T13:01:00+08:00</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405788</t>
+          <t>https://news.cnyes.com/news/id/6405698</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4/10 CPI開獎有多慘? 通膨預期與遞延發酵才是重點 | 鉅亨網 - 專家觀點</t>
+          <t>解放軍報披露：日本囤44.4噸分離鈽 夠製造5,500枚核彈頭 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-04-02 13:58</t>
+          <t>2026-04-02 12:29</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-02T13:58:26+08:00</t>
+          <t>2026-04-02T12:29:26+08:00</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405770</t>
+          <t>https://news.cnyes.com/news/id/6405672</t>
         </is>
       </c>
     </row>
@@ -1369,22 +1369,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>民主黨怒轟川普演說「混亂可悲」 對伊朗戰略是史上最大失敗 | 鉅亨網 - 國際政經</t>
+          <t>不排除地面戰、鎖海峽就重擊 川普演說全文、重點QA一次看 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-04-02 13:57</t>
+          <t>2026-04-02 11:41</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-02T13:57:52+08:00</t>
+          <t>2026-04-02T11:41:46+08:00</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405756</t>
+          <t>https://news.cnyes.com/news/id/6405625</t>
         </is>
       </c>
     </row>
@@ -1396,22 +1396,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>油價飆升惹民怨！民調：川普經濟支持率降至31% 創任內新低 | 鉅亨網 - 國際政經</t>
+          <t>高盛：全球避險基金3月回檔幅度創四年多之最 亞洲避險基金暴跌7.3%最慘 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-04-02 13:20</t>
+          <t>2026-04-02 11:40</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-02T13:20:08+08:00</t>
+          <t>2026-04-02T11:40:06+08:00</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405699</t>
+          <t>https://news.cnyes.com/news/id/6405209</t>
         </is>
       </c>
     </row>
@@ -1423,22 +1423,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>中東衝突成人民幣國際化破局之戰！德銀：石油美元面臨危機 人民幣迎來關鍵窗口期 | 鉅亨網 - 國際政經</t>
+          <t>最強救火隊集結！IEA、IMF、世銀發聯合聲明 將協調因應伊朗戰爭衝擊 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-04-02 13:20</t>
+          <t>2026-04-02 11:21</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-02T13:20:04+08:00</t>
+          <t>2026-04-02T11:21:32+08:00</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405195</t>
+          <t>https://news.cnyes.com/news/id/6405459</t>
         </is>
       </c>
     </row>
@@ -1450,22 +1450,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>美國低估伊朗？專家：伊朗戰爭恐比越戰更棘手 | 鉅亨網 - 國際政經</t>
+          <t>伊朗最高領袖：繼續封鎖荷姆茲海峽 研究開闢潛在戰線 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-04-02 13:01</t>
+          <t>2026-04-02 10:48</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-02T13:01:00+08:00</t>
+          <t>2026-04-02T10:48:52+08:00</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405698</t>
+          <t>https://news.cnyes.com/news/id/6405367</t>
         </is>
       </c>
     </row>
@@ -1477,22 +1477,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>解放軍報披露：日本囤44.4噸分離鈽 夠製造5,500枚核彈頭 | 鉅亨網 - 國際政經</t>
+          <t>以色列擔憂美國宣布伊朗戰爭結束 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-04-02 12:29</t>
+          <t>2026-04-02 10:32</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-04-02T12:29:26+08:00</t>
+          <t>2026-04-02T10:32:17+08:00</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405672</t>
+          <t>https://news.cnyes.com/news/id/6405354</t>
         </is>
       </c>
     </row>
@@ -1504,22 +1504,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>不排除地面戰、鎖海峽就重擊 川普演說全文、重點QA一次看 | 鉅亨網 - 國際政經</t>
+          <t>英特爾Intel(INTC-US)斥資142億美元重掌Fab 34，AI推論需求升溫下強化歐洲晶圓廠控制權 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-04-02 11:41</t>
+          <t>2026-04-02 10:30</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-02T11:41:46+08:00</t>
+          <t>2026-04-02T10:30:07+08:00</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405625</t>
+          <t>https://news.cnyes.com/news/id/6405521</t>
         </is>
       </c>
     </row>
@@ -1531,22 +1531,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>高盛：全球避險基金3月回檔幅度創四年多之最 亞洲避險基金暴跌7.3%最慘 | 鉅亨網 - 國際政經</t>
+          <t>川普暗示對伊朗採取進一步軍事打擊 亞太股市齊步由漲轉跌 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-04-02 11:40</t>
+          <t>2026-04-02 10:25</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-04-02T11:40:06+08:00</t>
+          <t>2026-04-02T10:25:16+08:00</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405209</t>
+          <t>https://news.cnyes.com/news/id/6405508</t>
         </is>
       </c>
     </row>
@@ -1558,22 +1558,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>最強救火隊集結！IEA、IMF、世銀發聯合聲明 將協調因應伊朗戰爭衝擊 | 鉅亨網 - 國際政經</t>
+          <t>美以伊衝突重塑全球液化天然氣貿易格局 澳洲迎千載難逢機會 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-04-02 11:21</t>
+          <t>2026-04-02 10:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-04-02T11:21:32+08:00</t>
+          <t>2026-04-02T10:00:13+08:00</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405459</t>
+          <t>https://news.cnyes.com/news/id/6404838</t>
         </is>
       </c>
     </row>
@@ -1585,22 +1585,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>伊朗最高領袖：繼續封鎖荷姆茲海峽 研究開闢潛在戰線 | 鉅亨網 - 國際政經</t>
+          <t>哈薩克：繼續向中國轉運俄羅斯原油 美國准了 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-04-02 10:48</t>
+          <t>2026-04-02 09:54</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-04-02T10:48:52+08:00</t>
+          <t>2026-04-02T09:54:31+08:00</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405367</t>
+          <t>https://news.cnyes.com/news/id/6405219</t>
         </is>
       </c>
     </row>
@@ -1612,22 +1612,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>以色列擔憂美國宣布伊朗戰爭結束 | 鉅亨網 - 國際政經</t>
+          <t>川普發表演說 稱對伊朗戰爭取得壓倒性勝利 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-04-02 10:32</t>
+          <t>2026-04-02 09:25</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-04-02T10:32:17+08:00</t>
+          <t>2026-04-02T09:25:54+08:00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405354</t>
+          <t>https://news.cnyes.com/news/id/6405336</t>
         </is>
       </c>
     </row>
@@ -1639,22 +1639,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>英特爾Intel(INTC-US)斥資142億美元重掌Fab 34，AI推論需求升溫下強化歐洲晶圓廠控制權 | 鉅亨網 - 國際政經</t>
+          <t>中東戰火延燒 成本壓力爆表 英國企業信心創6年最長跌勢 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-04-02 10:30</t>
+          <t>2026-04-02 09:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-04-02T10:30:07+08:00</t>
+          <t>2026-04-02T09:00:10+08:00</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405521</t>
+          <t>https://news.cnyes.com/news/id/6405177</t>
         </is>
       </c>
     </row>
@@ -1666,22 +1666,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>川普暗示對伊朗採取進一步軍事打擊 亞太股市齊步由漲轉跌 | 鉅亨網 - 國際政經</t>
+          <t>晶片再强也白搭？美AI資料中心建設潮遭遇「變壓器荒」 中國供應鏈卡住脖子 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-04-02 10:25</t>
+          <t>2026-04-02 09:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-04-02T10:25:16+08:00</t>
+          <t>2026-04-02T09:00:08+08:00</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405508</t>
+          <t>https://news.cnyes.com/news/id/6403979</t>
         </is>
       </c>
     </row>
@@ -1693,22 +1693,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>美以伊衝突重塑全球液化天然氣貿易格局 澳洲迎千載難逢機會 | 鉅亨網 - 國際政經</t>
+          <t>供應告急！全球鋁庫存可用天數恐降至45天 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-04-02 10:00</t>
+          <t>2026-04-02 08:35</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-04-02T10:00:13+08:00</t>
+          <t>2026-04-02T08:35:57+08:00</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404838</t>
+          <t>https://news.cnyes.com/news/id/6405196</t>
         </is>
       </c>
     </row>
@@ -1720,265 +1720,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>哈薩克：繼續向中國轉運俄羅斯原油 美國准了 | 鉅亨網 - 國際政經</t>
+          <t>尹錫悅看守所內「吸金」12億韓元 比李在明年薪高數倍 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-04-02 09:54</t>
+          <t>2026-04-02 08:24</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-04-02T09:54:31+08:00</t>
+          <t>2026-04-02T08:24:12+08:00</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405219</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>鉅亨網</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>川普發表演說 稱對伊朗戰爭取得壓倒性勝利 | 鉅亨網 - 國際政經</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2026-04-02 09:25</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2026-04-02T09:25:54+08:00</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>https://news.cnyes.com/news/id/6405336</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>鉅亨網</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>中東戰火延燒 成本壓力爆表 英國企業信心創6年最長跌勢 | 鉅亨網 - 國際政經</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2026-04-02 09:00</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2026-04-02T09:00:10+08:00</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>https://news.cnyes.com/news/id/6405177</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>鉅亨網</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>晶片再强也白搭？美AI資料中心建設潮遭遇「變壓器荒」 中國供應鏈卡住脖子 | 鉅亨網 - 國際政經</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2026-04-02 09:00</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2026-04-02T09:00:08+08:00</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>https://news.cnyes.com/news/id/6403979</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>鉅亨網</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>供應告急！全球鋁庫存可用天數恐降至45天 | 鉅亨網 - 國際政經</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2026-04-02 08:35</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2026-04-02T08:35:57+08:00</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>https://news.cnyes.com/news/id/6405196</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>鉅亨網</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>尹錫悅看守所內「吸金」12億韓元 比李在明年薪高數倍 | 鉅亨網 - 國際政經</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2026-04-02 08:24</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2026-04-02T08:24:12+08:00</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
           <t>https://news.cnyes.com/news/id/6405184</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>鉅亨網</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>伊朗外交部：最高領袖身體健康 因戰爭推遲公開露面 | 鉅亨網 - 國際政經</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2026-04-02 08:15</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2026-04-02T08:15:37+08:00</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>https://news.cnyes.com/news/id/6405183</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>鉅亨網</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>川普：美軍「很快」就會撤離伊朗 但必要時仍會「點狀打擊」 | 鉅亨網 - 國際政經</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2026-04-02 07:20</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2026-04-02T07:20:03+08:00</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>https://news.cnyes.com/news/id/6405092</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>鉅亨網</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>紐時：美軍增派18架A-10攻擊機 中東艦隊規模即將翻倍 | 鉅亨網 - 國際政經</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2026-04-02 06:52</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2026-04-02T06:52:34+08:00</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>https://news.cnyes.com/news/id/6405107</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>鉅亨網</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>伊朗最高領袖穆吉塔巴最新聲明：力挺真主黨 重申對抗「美以」立場 | 鉅亨網 - 國際政經</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2026-04-02 06:40</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2026-04-02T06:40:48+08:00</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>https://news.cnyes.com/news/id/6405133</t>
         </is>
       </c>
     </row>
